--- a/kawasaki_project/05_試算・管理シート/川崎町_認知症の人の数の推計_R8.10.19.xlsx
+++ b/kawasaki_project/05_試算・管理シート/川崎町_認知症の人の数の推計_R8.10.19.xlsx
@@ -15,7 +15,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_簡便法との比較" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_検算（全国で戻るか）" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_国が求めているもの" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_残る前提・未実施" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_将来の推計（暫定）" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_町にお願いしたいこと" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_残る前提・未実施" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -100,7 +102,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -122,6 +124,12 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -736,6 +744,304 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="56" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>将来の推計を確かなものにするために、町にお願いしたいこと</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="60" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>10シートの暫定の推計を、按分のいらない確かな推計に置き換えるための手順です。⚠ **見える化システムの操作は町が進める範囲ですので、当方では触れていません。**</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>順</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>お願いしたいこと</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>なぜ要るか</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>どこにあるか</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>見える化システムから「自然体推計の計算過程確認シート」を出力し、ご提供いただきたい（総括表と同じ推計パターンで）</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>⚠ **同シートの「2.1 総人口と被保険者数」に、令和12・17・22・27・32年度の第1号被保険者数が**性・年齢5歳階級別（65〜69／70〜74／75〜79／80〜84／85〜89／90歳以上）**で載ります。** これがあれば按分は一切不要になり、現在（令和8年）と同じ方法で将来まで一貫して算出できます。</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>国「自然体推計の計算過程確認シートのガイド」2.1 総人口と被保険者数 2)被保険者数（09_元資料/その他データ）。⚠ 当方が持つガイドは第9期向けの版で、人口の出所を「日本の地域別将来推計人口（平成30年3月推計）」と書いている。第10期は令和5年推計による</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>⚠ **総括表には3区分しか載りません。**総括表の再出力ではなく、**別のシート**です</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>町からご提供いただいた総括表（令和8年10月19日出力）の5_保険料推計 行111〜115 にある前期（65〜74歳）・後期（75〜84歳）・後期（85歳〜）が、総括表に載る唯一の年齢の内訳です。有病率は6階級で公表されているため、3区分のままでは当てられません。</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>総括表 5_保険料推計 行111〜115</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>（参考）見える化の画面では、既に6階級で表示されています</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>令和8年9月11日にいただいた画面の控えでは、認定者数の実績値（令和8年度）も施策反映（令和9年度推計値）も、男・女・合計それぞれ65〜69歳から90歳以上までの6階級で表示されています。システムは6階級の値を持っています。</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>09_元資料/R8実績データ/R8.9.11受領版/見える化システム画面キャプチャ_R8.9.11_4.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>認定調査の日常生活自立度Ⅱ以上の実数（令和6・7年度）</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>推計値（本シート）と実数は測るものが違い、差が認定を受けておられない認知症の方のおおよその規模になります。</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>確認事項No.157</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="56" customWidth="1" min="3" max="3"/>
+    <col width="62" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>残る前提と、行っていないこと（「未実施」を「適合」に丸めない）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="60" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>本シートで**行えなかったこと**を件数と理由として残します。数を合わせるために推測の値を置いてはいません。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>件</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>行えなかったこと</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>なぜ行えないか</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>どうすれば行えるか</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>将来（令和12・17・22年度）の推計を、按分なしで行うこと</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>⚠ **暫定の推計は09シートに出しました**（令和12年度424人・令和17年度457人・令和22年度487人）。ただし町からご提供いただいた将来の人口は**3区分**（前期65〜74歳／後期75〜84歳／後期85歳〜）しかなく、有病率は6階級で公表されているため、区分の中の内訳を当方で置いています。置き方によって約8％（35〜40人）振れます。⚠ 社人研「日本の地域別将来推計人口（令和5年推計）」はwww.ipss.go.jp にあり、当方の環境から接続できません</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>⚠ **見える化システムの「自然体推計の計算過程確認シート」をご出力いただければ、按分は一切不要になります**（10シート）。同シートは性・年齢5歳階級別の第1号被保険者数（令和12・17・22・27・32年度）を持ちます。算定は 07_ソーススクリプト/calc_ninchisho_shorai_R8.10.19.py にあり、人口の表を差し替えるだけです。⚠ 国は「性年齢階級別有病率が今後も一定と仮定」しているため、有病率は据え置きます</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>認定調査の日常生活自立度Ⅱ以上の実数（令和6・7年度）</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>町からのご提供を待っています（確認事項No.157）</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>ご提供いただければ、推計値と並べて掲げ、差（＝認定を受けていない認知症の方の規模）をお示しします</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>見える化システムによる裏づけ</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>⚠ **当方で直接データを触る想定ではありません。**ＩＤ・パスワードはお預かりしていますが、見える化対応は町が進める範囲です。なお全国課長会議資料52頁は、事項十一の把握方法を「各自治体で把握」としており、**見える化システムは挙げられていません**（08シート）</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>見える化システムに認知症の人の数・推計値が搭載されているかどうかを町でご確認ください。載っていれば突合します。載っていなければ、本シートの推計値がその欄に当たります</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>有病率の研究報告書本体との突合</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>基本指針（案）76頁がいう「先行研究」の本体（九州大学の研究報告書）は www.eph.med.kyushu-u.ac.jp にあり、当方の環境から接続できません。当方が用いたのは厚生労働省が作成した要約資料です</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>厚生労働省の資料は国自身が用いている基礎数値ですので、計画に載せる出典としてはこれで足ります。⚠ 出典の表記は「厚生労働省」とし、研究名・研究代表者を併記します</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>基本指針の告示の確認</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>⚠ **当方が確かめられた最新の原文は令和8年6月29日の「基本指針（案）について（新旧案）」です。**告示が出たかを確かめられていません</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>官報・介護保険最新情報で町とご確認ください。告示で別表一の文言が変わった場合は、08シートを改めます</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -2763,154 +3069,552 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:H29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="56" customWidth="1" min="3" max="3"/>
-    <col width="62" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>残る前提と、行っていないこと（「未実施」を「適合」に丸めない）</t>
+          <t>将来の認知症の人の数（令和12・17・22年度）　— ⚠ 暫定</t>
         </is>
       </c>
     </row>
     <row r="2" ht="60" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>本シートで**行えなかったこと**を件数と理由として残します。数を合わせるために推測の値を置いてはいません。</t>
+          <t>⚠ **暫定です。** 有病率は6つの年齢階級で公表されているのに対し、町からご提供いただいた将来の人口は**3区分**（前期65〜74歳／後期75〜84歳／後期85歳〜）しかありません。区分の中の内訳は、町の1歳刻みの人口（令和8年6月末）を年齢進行させ、全国の死亡率（令和6年）を当てて求め、3区分の合計が町のご提供の値に一致するよう比例調整しています（方法Ｃ2）。⚠ **正道は按分しないことです。**見える化システムの「自然体推計の計算過程確認シート」は、性・年齢5歳階級別の第1号被保険者数（令和12・17・22・27・32年度）を持ちます。ご出力いただければ按分は要りません（10シート）。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>件</t>
+          <t>年度</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>行えなかったこと</t>
+          <t>65歳以上人口</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>なぜ行えないか</t>
+          <t>認知症の人の数</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>どうすれば行えるか</t>
+          <t>65歳以上に占める割合</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>ＭＣＩの人の数</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>割合</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>合計</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>割合</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="B5" s="7" t="inlineStr">
-        <is>
-          <t>将来（令和12・17・22年度）の認知症の人の数の推計</t>
-        </is>
-      </c>
-      <c r="C5" s="7" t="inlineStr">
-        <is>
-          <t>年齢階級別の**将来**人口が要ります。本町の計画が用いている国立社会保障・人口問題研究所「日本の地域別将来推計人口（令和5年推計）」は5歳階級別の将来人口を持ちますが、当方の作業環境から www.ipss.go.jp に接続できません。地域包括ケア「見える化」システムは町が進める範囲です</t>
-        </is>
-      </c>
-      <c r="D5" s="7" t="inlineStr">
-        <is>
-          <t>⚠ **町で5歳階級別の将来人口（令和12・17・22年）をご用意いただければ、同じ式でその日のうちに将来値まで出せます。**算定は 07_ソーススクリプト/calc_ninchisho_R8.10.19.py にあり、人口の表を差し替えるだけです。⚠ 国は「性年齢階級別有病率が今後も一定と仮定」しているため、有病率は据え置きます</t>
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>令和8年度（現在・住民基本台帳）</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>3,209人</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>374人</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>11.7％</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>474人</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>14.8％</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>848人</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>26.4％</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="B6" s="7" t="inlineStr">
-        <is>
-          <t>認定調査の日常生活自立度Ⅱ以上の実数（令和6・7年度）</t>
-        </is>
-      </c>
-      <c r="C6" s="7" t="inlineStr">
-        <is>
-          <t>町からのご提供を待っています（確認事項No.157）</t>
-        </is>
-      </c>
-      <c r="D6" s="7" t="inlineStr">
-        <is>
-          <t>ご提供いただければ、推計値と並べて掲げ、差（＝認定を受けていない認知症の方の規模）をお示しします</t>
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>令和12年度（第1号被保険者数）</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>3,149人</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>424人</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>13.5％</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>504人</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>16.0％</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>928人</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>29.5％</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="n">
-        <v>3</v>
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>令和17年度（第1号被保険者数）</t>
+        </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>見える化システムによる裏づけ</t>
+          <t>2,967人</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>⚠ **当方で直接データを触る想定ではありません。**ＩＤ・パスワードはお預かりしていますが、見える化対応は町が進める範囲です。なお全国課長会議資料52頁は、事項十一の把握方法を「各自治体で把握」としており、**見える化システムは挙げられていません**（08シート）</t>
+          <t>457人</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>見える化システムに認知症の人の数・推計値が搭載されているかどうかを町でご確認ください。載っていれば突合します。載っていなければ、本シートの推計値がその欄に当たります</t>
+          <t>15.4％</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>516人</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>17.4％</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>973人</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>32.8％</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>有病率の研究報告書本体との突合</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>基本指針（案）76頁がいう「先行研究」の本体（九州大学の研究報告書）は www.eph.med.kyushu-u.ac.jp にあり、当方の環境から接続できません。当方が用いたのは厚生労働省が作成した要約資料です</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>厚生労働省の資料は国自身が用いている基礎数値ですので、計画に載せる出典としてはこれで足ります。⚠ 出典の表記は「厚生労働省」とし、研究名・研究代表者を併記します</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>基本指針の告示の確認</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>⚠ **当方が確かめられた最新の原文は令和8年6月29日の「基本指針（案）について（新旧案）」です。**告示が出たかを確かめられていません</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>官報・介護保険最新情報で町とご確認ください。告示で別表一の文言が変わった場合は、08シートを改めます</t>
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>令和22年度（第1号被保険者数）</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>2,835人</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>487人</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>17.2％</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>498人</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>17.6％</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>984人</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>34.7％</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>⚠ **母集団が違います。**現在は住民基本台帳の65歳以上人口（3,209人・令和8年6月末）、将来は第1号被保険者数です。令和8年度で48人（1.5％）違います。**割合（％）は母集団に依らない指標ですので、こちらで比べてください。**</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>▶ 区分の中の内訳の置き方による振れ（認知症の人の数）</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>年度</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>Ａ 現在の構成で固定</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>Ｃ1 年齢進行（死亡率なし）</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="inlineStr">
+        <is>
+          <t>Ｃ2 年齢進行（死亡率あり）</t>
+        </is>
+      </c>
+      <c r="E14" s="9" t="inlineStr">
+        <is>
+          <t>簡便法 第1号×全国の有病率</t>
+        </is>
+      </c>
+      <c r="F14" s="9" t="inlineStr">
+        <is>
+          <t>振れ（Ａ〜Ｃ1）</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>令和12年度</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>398人</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>432人</t>
+        </is>
+      </c>
+      <c r="D15" s="10" t="inlineStr">
+        <is>
+          <t>424人</t>
+        </is>
+      </c>
+      <c r="E15" s="11" t="inlineStr">
+        <is>
+          <t>447人</t>
+        </is>
+      </c>
+      <c r="F15" s="8" t="inlineStr">
+        <is>
+          <t>8.0％</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>令和17年度</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>444人</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>479人</t>
+        </is>
+      </c>
+      <c r="D16" s="10" t="inlineStr">
+        <is>
+          <t>457人</t>
+        </is>
+      </c>
+      <c r="E16" s="11" t="inlineStr">
+        <is>
+          <t>442人</t>
+        </is>
+      </c>
+      <c r="F16" s="8" t="inlineStr">
+        <is>
+          <t>7.7％</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>令和22年度</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>472人</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>512人</t>
+        </is>
+      </c>
+      <c r="D17" s="10" t="inlineStr">
+        <is>
+          <t>487人</t>
+        </is>
+      </c>
+      <c r="E17" s="11" t="inlineStr">
+        <is>
+          <t>422人</t>
+        </is>
+      </c>
+      <c r="F17" s="8" t="inlineStr">
+        <is>
+          <t>8.2％</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>⚠ **Ａ（現在の構成で固定）は採りません。**本町の75〜84歳の現在の内訳（75〜79歳784人・80〜84歳354人）は、団塊の世代と終戦前後の出生の落ち込みが隣り合った一過性の姿で、年とともに反転します。Ａはこの歪みを将来まで凍結します。</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>⚠ **簡便法（第1号被保険者数×全国の有病率）は採れません。**令和22年度が令和12年度より**少なく**出ます。85歳以上の人口は605人→893人と増えるのに減るのは、年齢構成を無視したことによる見かけの減です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>⚠ 死亡率の置き方（0.7〜1.4倍に振っても±2％）より、**内訳の置き方（約8％）の方が大きく効きます。**だからこそ6階級の将来人口を町からいただくのが正道です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>▶ 85歳以上の中身（終戦前後の出生の落ち込みの通過）</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="12" t="inlineStr">
+        <is>
+          <t>年度</t>
+        </is>
+      </c>
+      <c r="B24" s="12" t="inlineStr">
+        <is>
+          <t>85〜89歳</t>
+        </is>
+      </c>
+      <c r="C24" s="12" t="inlineStr">
+        <is>
+          <t>90歳以上</t>
+        </is>
+      </c>
+      <c r="D24" s="12" t="inlineStr">
+        <is>
+          <t>90歳以上の割合</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t>令和8年度</t>
+        </is>
+      </c>
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t>351人</t>
+        </is>
+      </c>
+      <c r="C25" s="8" t="inlineStr">
+        <is>
+          <t>234人</t>
+        </is>
+      </c>
+      <c r="D25" s="8" t="inlineStr">
+        <is>
+          <t>40.0％</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="8" t="inlineStr">
+        <is>
+          <t>令和12年度</t>
+        </is>
+      </c>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>304人</t>
+        </is>
+      </c>
+      <c r="C26" s="8" t="inlineStr">
+        <is>
+          <t>301人</t>
+        </is>
+      </c>
+      <c r="D26" s="8" t="inlineStr">
+        <is>
+          <t>49.7％</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="8" t="inlineStr">
+        <is>
+          <t>令和17年度</t>
+        </is>
+      </c>
+      <c r="B27" s="8" t="inlineStr">
+        <is>
+          <t>493人</t>
+        </is>
+      </c>
+      <c r="C27" s="8" t="inlineStr">
+        <is>
+          <t>266人</t>
+        </is>
+      </c>
+      <c r="D27" s="8" t="inlineStr">
+        <is>
+          <t>35.1％</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="8" t="inlineStr">
+        <is>
+          <t>令和22年度</t>
+        </is>
+      </c>
+      <c r="B28" s="8" t="inlineStr">
+        <is>
+          <t>525人</t>
+        </is>
+      </c>
+      <c r="C28" s="8" t="inlineStr">
+        <is>
+          <t>368人</t>
+        </is>
+      </c>
+      <c r="D28" s="8" t="inlineStr">
+        <is>
+          <t>41.2％</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>⚠ **90歳以上の割合は令和17年度にいったん下がります。**終戦前後の出生の落ち込み（令和8年に79〜89歳・1歳あたり約70人。直前の団塊は1歳あたり約171人）が90歳以上の階級を通る時期に当たるためです。その後に団塊の世代が85歳以上へ入り、**施策の山場は令和17年度以降に来ます。**</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A2:D2"/>
+  <mergeCells count="11">
+    <mergeCell ref="A12:H12"/>
+    <mergeCell ref="A21:H21"/>
+    <mergeCell ref="A29:H29"/>
+    <mergeCell ref="A20:H20"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A10:H10"/>
+    <mergeCell ref="A13:H13"/>
+    <mergeCell ref="A11:H11"/>
+    <mergeCell ref="A19:H19"/>
+    <mergeCell ref="A23:H23"/>
+    <mergeCell ref="A22:H22"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
